--- a/artfynd/A 22647-2022 artfynd.xlsx
+++ b/artfynd/A 22647-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22647-2022 artfynd.xlsx
+++ b/artfynd/A 22647-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1814,6 +1814,113 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122693954</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Koskilamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>496184</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6811863</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jonas Karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Jonas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22647-2022 artfynd.xlsx
+++ b/artfynd/A 22647-2022 artfynd.xlsx
@@ -1819,7 +1819,7 @@
         <v>122693954</v>
       </c>
       <c r="B12" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 22647-2022 artfynd.xlsx
+++ b/artfynd/A 22647-2022 artfynd.xlsx
@@ -1819,7 +1819,7 @@
         <v>122693954</v>
       </c>
       <c r="B12" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 22647-2022 artfynd.xlsx
+++ b/artfynd/A 22647-2022 artfynd.xlsx
@@ -1819,7 +1819,7 @@
         <v>122693954</v>
       </c>
       <c r="B12" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 22647-2022 artfynd.xlsx
+++ b/artfynd/A 22647-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101624783</v>
+        <v>101624540</v>
       </c>
       <c r="B2" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496189.5385572455</v>
+        <v>496167</v>
       </c>
       <c r="R2" t="n">
-        <v>6811985.793818079</v>
+        <v>6812108</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,52 +773,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101624955</v>
+        <v>101624687</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Orsa, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496174.086874302</v>
+        <v>496180</v>
       </c>
       <c r="R3" t="n">
-        <v>6811876.263612516</v>
+        <v>6812045</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,19 +842,9 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,19 +871,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101624974</v>
+        <v>101624879</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -943,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496189.8982154179</v>
+        <v>496154</v>
       </c>
       <c r="R4" t="n">
-        <v>6811876.724640843</v>
+        <v>6811921</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -976,19 +940,9 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,19 +969,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101625061</v>
+        <v>101624974</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1056,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496193.3153575105</v>
+        <v>496190</v>
       </c>
       <c r="R5" t="n">
-        <v>6811934.604319453</v>
+        <v>6811877</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1089,19 +1038,9 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,19 +1067,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101624879</v>
+        <v>101625002</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1169,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496153.5346151541</v>
+        <v>496200</v>
       </c>
       <c r="R6" t="n">
-        <v>6811921.253647882</v>
+        <v>6811934</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,19 +1136,9 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>101624540</v>
+        <v>101625061</v>
       </c>
       <c r="B7" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1282,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496167.1557467397</v>
+        <v>496193</v>
       </c>
       <c r="R7" t="n">
-        <v>6812108.277539161</v>
+        <v>6811935</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,19 +1234,9 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,15 +1263,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>101624505</v>
+        <v>101625179</v>
       </c>
       <c r="B8" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,21 +1274,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1299,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496149.4084709556</v>
+        <v>496207</v>
       </c>
       <c r="R8" t="n">
-        <v>6812089.1631807</v>
+        <v>6812122</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1428,19 +1332,9 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,61 +1361,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>101624916</v>
+        <v>101625217</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Orsa, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496147.7519322045</v>
+        <v>496201</v>
       </c>
       <c r="R9" t="n">
-        <v>6811891.122401515</v>
+        <v>6812102</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1551,19 +1430,9 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,37 +1459,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101624687</v>
+        <v>101624783</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496179.5431087101</v>
+        <v>496190</v>
       </c>
       <c r="R10" t="n">
-        <v>6812045.599815677</v>
+        <v>6811985</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1664,19 +1528,9 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,37 +1557,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101625217</v>
+        <v>101624505</v>
       </c>
       <c r="B11" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1744,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496201.1633784726</v>
+        <v>496149</v>
       </c>
       <c r="R11" t="n">
-        <v>6812101.543365117</v>
+        <v>6812089</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1777,19 +1626,9 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,57 +1655,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122693954</v>
+        <v>101624721</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Koskilamm, Dlr</t>
+          <t>Orsa, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496184</v>
+        <v>496145</v>
       </c>
       <c r="R12" t="n">
-        <v>6811863</v>
+        <v>6812014</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1890,12 +1721,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,22 +1735,532 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>101625010</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Orsa, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>496200</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6811934</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>101625206</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Orsa, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>496206</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6812110</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>101624916</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Orsa, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>496147</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6811891</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>101624955</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Orsa, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>496174</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6811877</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122693954</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Koskilamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>496184</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6811863</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Jonas Karlsson</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Via Jonas Karlsson</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22647-2022 artfynd.xlsx
+++ b/artfynd/A 22647-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101624540</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101624687</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101624879</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101624974</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101625002</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101625061</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101625179</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101625217</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101624783</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101624505</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1750,6 +1805,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101624721</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,6 +1908,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101625010</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1952,6 +2017,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101625206</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2060,6 +2130,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101624916</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2159,6 +2234,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101624955</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2261,8 +2341,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122693954</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>